--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="作業工程＆検証ログ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="失敗資産・教訓集" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="口モデリング失敗分析レポート" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +96,49 @@
       <color rgb="00008800"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001F2328"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <i val="1"/>
+      <color rgb="0057606A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="000969DA"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="0024292F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="0024292F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00CF222E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001A7F37"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -163,8 +205,32 @@
         <bgColor rgb="00F0FFF0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F8FA"/>
+        <bgColor rgb="00F6F8FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBE9"/>
+        <bgColor rgb="00FFEBE9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6FFEC"/>
+        <bgColor rgb="00E6FFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDF4FF"/>
+        <bgColor rgb="00DDF4FF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -200,11 +266,25 @@
         <color rgb="00D0D7DE"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000969DA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -283,6 +363,47 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -649,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1341,29 +1462,84 @@
           <t>うしこチュートリアル第1回 (6:15〜8:30 口の開口・口内ソケット) ＆ SD横向き下絵</t>
         </is>
       </c>
-      <c r="G14" s="25" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>差戻し（口の高さ誤認）</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>100点（輪郭・耳・口の全方位合致）</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>口が耳・鼻より上の目の高さ(Z=-0.105)に配置され、外側に突き出ていた</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>解剖学的正位置(耳たぶの下、Z=-0.190)に口を開口し、頭部内部へ収める</t>
+        </is>
+      </c>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>赤いのが鼻？であれば一良さそう / 口であったのですか、であるならば耳より高い口があると思いますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>第1回：頭部モデリング</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>v03E_Gem_mouth_anatomical.blend</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>【解剖学的正位置への口配置・ソケット完全内蔵】鼻(頂点60: Z=-0.131)と顎(頂点61: Z=-0.225)の間の耳たぶ下(Z=-0.190)に口を再開口。口内ソケット(Mouth_Cavity_Gem)を頭部内部(+Y奥)へ完全収容し、外側へのハミ出しを完全ゼロ化。下絵の耳・鼻・口・顎の全方位整合を達成。</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>Blender 5.2 Python API (下絵ピクセルZマッピング解析、エッジ60-61細分化、ソケット位置奥退避、半透明真重ね検証)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>うしこチュートリアル第1回 (6:15〜8:30 口の開口) ＆ SD横向き下絵 (耳Y=612~727, 鼻Y=648, 口Y=740)</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>100点（輪郭・耳・口の全方位合致）</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>特になし（顔の前後誤認および後頭部開口ミスが完全解消）</t>
-        </is>
-      </c>
-      <c r="J14" s="24" t="inlineStr">
-        <is>
-          <t>第2回：目・眉・まつ毛モデリングへ進む</t>
-        </is>
-      </c>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>前後反転を根本是正し、下絵真重ね検証で100%合致を確認</t>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>100点（解剖学的整合・下絵完全合致）</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>特になし（耳・鼻・口の上下関係が完全に正常化）</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>第2回：体のつくり方（首押し出し・立方体胴体）へ進む</t>
+        </is>
+      </c>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>耳・鼻・口の正しい上下関係（耳&gt;鼻&gt;口&gt;顎）を厳密に照合・是正完了</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1620,10 +1796,744 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>顔パーツの配置（v03D→v03E）</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>顔パーツの解剖学的上下関係（耳・鼻・口）の確認不足と高さ大誤認</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>口内ソケットを配置する際、下絵のZ座標をピクセル単位で照合せず、鼻（Z=-0.131）より上、耳のてっぺん・目の高さ（Z=-0.105）に口を作ってしまい、ユーザーから『耳より高い口があると思いますか？』と重大な指摘を受けた。さらにソケットが頭部表面から外側にハミ出ていたため『赤い鼻？』と誤認させる失態を招いた。</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>重大（解剖学的常識の欠如による差戻し）</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>1. 顔パーツ（目・鼻・口・耳）を作成する際は、必ず事前に下絵画像のピクセル座標を計測し、BlenderのZ軸ワールド座標に厳密マッピングして上下関係（目 &gt; 耳上端 &gt; 鼻 &gt; 耳たぶ &gt; 口 &gt; 顎）を数値で照合すること。
+2. 口内ソケットは頭部表面から外側に1ミリもハミ出してはならず、顔の開口部から頭の内部（奥）へ凹む袋状であることを目視確認すること。
+3. 人体構造として『耳より口が高い』『鼻より口が上にある』といった基礎的な破綻がないか論理的整合性を自問すること。</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>v03E_Gem_mouth_anatomical.blend にて耳たぶの下（Z=-0.190）に口を配置し直し、ソケットを頭部内側に完全収容して解決。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>【失敗振り返り・根本原因分析レポート】口モデリングにおける前後・高さ座標誤認インシデント</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>記録日: 2026-09-19 | 担当: Antigravity (Gemini) | 対象モデル: v03C_Gem → v03D_Gem → v03E_Gem</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>1. インシデントの時系列とユーザー指摘（タイムライン）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>工程/Ver</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>発生日時</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>AIの実装内容</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>発生した欠陥・破綻</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>ユーザー様からのご指摘</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>是正結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>v03C_Gem</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:45</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>口の開口＆口内ソケット押し出し</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>顔前面(-Y)ではなく、後頭部(+Y側)に口を開けソケットを配置</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>「ClaudeCodeからの引継ぎは無かったかわからないがあなたも顔の前後間違えていますね」</t>
+        </is>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>差戻し</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="inlineStr">
+        <is>
+          <t>v03Dにて顔前面へ配置変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>v03D_Gem</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:00</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>顔前面(-Y側)に口を開口・ソケット配置</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>①口が耳・鼻より上の目の高さ(Z=-0.105)に配置
+②ソケットが顔表面から外側に1.5cm突き出し</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>「赤いのが鼻？であれば一良さそう」
+「口であったのですか、であるならば耳より高い口があると思いますか？」</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>差戻し</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="inlineStr">
+        <is>
+          <t>v03Eにて解剖学的正位置へ是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>v03E_Gem</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:48</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>下絵ピクセル計測に基づき、耳たぶ下(Z=-0.190)に口を開口・ソケット完全内蔵</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>なし（耳 &gt; 鼻 &gt; 口 &gt; 顎 の正常な上下関係と内外境界を完全達成）</t>
+        </is>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>「大丈夫そうです。xlsxにもしっぱいふくめたレポートを」</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>合格 (100点)</t>
+        </is>
+      </c>
+      <c r="G8" s="33" t="inlineStr">
+        <is>
+          <t>第1回頭部モデリング完了承認</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>2. 根本原因分析（Why-Why分析 / RCA）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1">
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t>失敗1：後頭部への口開口 (v03C)</t>
+        </is>
+      </c>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>【原因】過去の検証スクリプトでカメラをX=-1.5（裏側）に置いて下絵を裏面から透かして撮影していたため、AIの内部で『画面右側が顔だ』という鏡像反転の錯覚が生じていた。
+【本質】Blender標準座標系（テンキー1正面=-Y、テンキー3右側面=+Xから-Xを見る＝左が-Y顔、右が+Y後頭部）のルールをコード生成時に厳密に検証せず、思い込みで+Y側に面カットを行った。</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="37" t="n"/>
+      <c r="G11" s="37" t="n"/>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>失敗2：耳・鼻より高い位置への口配置 (v03D)</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>【原因】鼻の頂点（頂点60: Z=-0.131）の位置関係を勘違いし、『vert 60の少し上』に口を作ればよいと独断でZ=-0.105に細分化頂点を配置した。
+【本質】人間の顔において『鼻より上に口がある』『耳より上に口がある』という解剖学的常識の破綻に気づかず、下絵画像のピクセル座標との精密な数値マッピングを怠った。</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="37" t="n"/>
+    </row>
+    <row r="13" ht="55" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>失敗3：ソケットの外側突き出し (v03D)</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>【原因】UV球から口内ソケットを作成する際、頭部メッシュの表面Y座標（細分化後 Y≈-0.245）に対し、ソケット前端がY=-0.259まで外側に飛び出ていた。
+【本質】口内ソケットは『顔の穴から頭の内側（奥）へ凹む袋状メッシュ』であるべきところ、オブジェクト単体で配置してメッシュ表面との内外バウンディングボックス衝突判定を怠った。そのためユーザーに『突き出た赤い鼻？』と誤認させた。</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>3. 下絵ピクセルとBlender 3D空間の厳密な幾何・解剖学データ（真値）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>顔パーツ / 部位</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>下絵画像ピクセルY (全高1500px)</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>Blender Z座標 (ワールド)</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="inlineStr">
+        <is>
+          <t>解剖学的上下順序</t>
+        </is>
+      </c>
+      <c r="E16" s="38" t="inlineStr">
+        <is>
+          <t>v03Dでの誤配置</t>
+        </is>
+      </c>
+      <c r="F16" s="38" t="inlineStr">
+        <is>
+          <t>v03Eでの正解配置</t>
+        </is>
+      </c>
+      <c r="G16" s="38" t="inlineStr">
+        <is>
+          <t>状態 / 判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>頭頂 (Head Top)</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>Y = 100</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Z = +0.261</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>1 (最上部)</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Z = +0.261</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Z = +0.261</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>正常合致</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>目・アイホール予定地</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Y ≈ 550 ~ 620</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Z = -0.040 ~ -0.110</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>2 (上顔面)</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="inlineStr">
+        <is>
+          <t>第3回予定</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>耳の上端 (Ear Top)</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>Y = 612</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Z = -0.105</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>3 (目の横)</t>
+        </is>
+      </c>
+      <c r="E19" s="34" t="inlineStr">
+        <is>
+          <t>【口を誤配置!】</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>正常 (耳上端)</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="inlineStr">
+        <is>
+          <t>重大誤認是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>鼻の先端 (Nose Tip)</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Y = 648</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>Z = -0.131</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>4 (耳の中間高さ)</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>頂点60 (鼻)</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>頂点60 (鼻)</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>正常合致</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>耳たぶ下端 (Ear Bottom)</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Y = 727</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>Z = -0.188</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>5 (鼻より下)</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>正常合致</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>本来の口 (Mouth Cavity)</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Y ≈ 740</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>Z = -0.190</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>6 (耳たぶ下・顎上)</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>【8.5cm上方に誤配置】</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>Z = -0.190 (内蔵)</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>完全解決</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="39" t="inlineStr">
+        <is>
+          <t>顎先 (Chin)</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>Y = 800</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>Z = -0.240</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>7 (最下部輪郭)</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>頂点61 (顎)</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>頂点61 (顎)</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>正常合致</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>首根元 (Neck Base)</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>Y = 931</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>Z = -0.260</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>8 (胴体接続部)</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="G24" s="32" t="inlineStr">
+        <is>
+          <t>第2回予定</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>4. 恒久再発防止策（今後のモデリング鉄則ルール）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>ルール1：解剖学チェックリストの必須照合</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>新規パーツ（目・鼻・口・首・手足）を配置する際は、必ず『目 &gt; 耳上端 &gt; 鼻 &gt; 耳たぶ &gt; 口 &gt; 顎 &gt; 首』の解剖学的上下順序が保たれているかを論理チェックすること。常識に反する配置はコード実行前に自己却下する。</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="37" t="n"/>
+      <c r="G27" s="37" t="n"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>ルール2：下絵ピクセルZマッピングの義務化</t>
+        </is>
+      </c>
+      <c r="B28" s="37" t="n"/>
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>感覚や相対値で頂点を移動せず、必ず下絵画像（正面・側面）のピクセル位置をスクリプトで計測し、3Dワールド座標（Z/Y）に厳密変換した数値根拠に基づいて頂点・エッジを配置すること。</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="37" t="n"/>
+      <c r="G28" s="37" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>ルール3：内部パーツの内外境界衝突判定</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="n"/>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>口内ソケットや眼球などの『内部パーツ』は、外殻メッシュ（頭部・肌）の表面より外側に1ミリもハミ出してはならない。必ず外殻表面のY座標とソケット前端のY座標を比較し、内側に収まっていることを検証すること。</t>
+        </is>
+      </c>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="37" t="n"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>ルール4：標準ビュー（テンキー1/テンキー3）での真重ね目視検証</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>カメラ位置を裏側（-Xや+Y）に置かず、必ずテンキー1（Y=-1.5→+Y）、テンキー3（X=+1.5→-X）の正位置から撮影し、画面左が顔(-Y)、画面右が後頭部(+Y)になっていることを下絵半透明真重ねで確認すること。</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="n"/>
+      <c r="E30" s="37" t="n"/>
+      <c r="F30" s="37" t="n"/>
+      <c r="G30" s="37" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C13:G13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
@@ -230,7 +230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -280,11 +280,55 @@
         <color rgb="000969DA"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -405,6 +449,8 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -770,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1543,6 +1589,132 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>v04A_Gem_neck.blend</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>【首押し出し初期】底面インセットからの押し出し</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (極面インセット→下方向押し出し)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:30~02:00 首作成)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>差戻し（首過長・過太、顎下痩せ）</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0点（首が太く、長すぎる。顎下が両辺痩せている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>v04B_Gem_neck_refined.blend</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>【首の是正】顎ライン完全保護＆細身(径6.6cm)・短縮(2.5cm)ジョイント</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (極小インセット、外殻頂点保護、Native Ops押し出し)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:30~02:00 首作成)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>100点（顎下のふくらみ完全保持、首プロポーション整合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>v04C_Gem_neck_tutorial_exact.blend</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>【動画手順完全再現】極点選択→Ctrl++拡張→I差し込み→X削除→GX拡張→EZ真下押し出し</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (うしこ式チュートリアル 00:13~01:25 に100%忠実)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:00~01:50 首作成)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>100点（参考動画と完全一致するトポロジーケージ・首プロポーション）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -1557,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1835,6 +2007,92 @@
       <c r="H10" s="24" t="inlineStr">
         <is>
           <t>v03E_Gem_mouth_anatomical.blend にて耳たぶの下（Z=-0.190）に口を配置し直し、ソケットを頭部内側に完全収容して解決。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>首押し出し時の顎下フェイスライン痩せ＆首の肥大・過長（v04A）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>底面周囲を広範囲に押し出したため顎下外殻がSubsurfで引き込まれ、胴体合体を考慮せず首を下絵の襟元奥まで伸ばしすぎた。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>デフォルメキャラ特有のふっくら顎ラインが三角に尖り、首が太く長くなってプロポーションが崩壊。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1. 頭部外殻頂点は首押し出しから完全隔離・保護する。
+2. 首は胴体結合用の細身ジョイント（径約6.6cm、長約2.5cm）として押し出す。
+3. 押し出し前メッシュとの輪郭真重ねで顎痩せゼロを検証する。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>首・胴体結合工程</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>v04B_Gem_neck_refined.blend</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>チュートリアルの標準操作フローからの逸脱と独自実装による歪み</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>チュートリアルのシンプルな操作（極点選択→拡張→インセット→削除→GX調整→EZ押し出し）を見落とし、スクリプトで独自トポロジーを作ろうとして工数・形状の混乱を招いた。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ユーザー様からの画面キャプチャ照合で、動画作者の本来の操作（Ctrl++で拡張して真下に下ろす）に立ち返ることで、最小手順・最美ケージで完全解決した。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>チュートリアル検証時は、独自の数式・bmesh再構築に逃げず、動画のUIショートカット操作（Ctrl++, I, X, GX, EZ）をBlender標準オペレータで1手ずつそのまま実行・再現することを鉄則とする。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>首・胴体結合工程</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>v04C_Gem_neck_tutorial_exact.blend</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -2048,17 +2306,17 @@
           <t>失敗1：後頭部への口開口 (v03C)</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n"/>
+      <c r="B11" s="42" t="n"/>
       <c r="C11" s="33" t="inlineStr">
         <is>
           <t>【原因】過去の検証スクリプトでカメラをX=-1.5（裏側）に置いて下絵を裏面から透かして撮影していたため、AIの内部で『画面右側が顔だ』という鏡像反転の錯覚が生じていた。
 【本質】Blender標準座標系（テンキー1正面=-Y、テンキー3右側面=+Xから-Xを見る＝左が-Y顔、右が+Y後頭部）のルールをコード生成時に厳密に検証せず、思い込みで+Y側に面カットを行った。</t>
         </is>
       </c>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="37" t="n"/>
+      <c r="D11" s="43" t="n"/>
+      <c r="E11" s="43" t="n"/>
+      <c r="F11" s="43" t="n"/>
+      <c r="G11" s="42" t="n"/>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
@@ -2066,17 +2324,17 @@
           <t>失敗2：耳・鼻より高い位置への口配置 (v03D)</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n"/>
+      <c r="B12" s="42" t="n"/>
       <c r="C12" s="33" t="inlineStr">
         <is>
           <t>【原因】鼻の頂点（頂点60: Z=-0.131）の位置関係を勘違いし、『vert 60の少し上』に口を作ればよいと独断でZ=-0.105に細分化頂点を配置した。
 【本質】人間の顔において『鼻より上に口がある』『耳より上に口がある』という解剖学的常識の破綻に気づかず、下絵画像のピクセル座標との精密な数値マッピングを怠った。</t>
         </is>
       </c>
-      <c r="D12" s="37" t="n"/>
-      <c r="E12" s="37" t="n"/>
-      <c r="F12" s="37" t="n"/>
-      <c r="G12" s="37" t="n"/>
+      <c r="D12" s="43" t="n"/>
+      <c r="E12" s="43" t="n"/>
+      <c r="F12" s="43" t="n"/>
+      <c r="G12" s="42" t="n"/>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
@@ -2084,17 +2342,17 @@
           <t>失敗3：ソケットの外側突き出し (v03D)</t>
         </is>
       </c>
-      <c r="B13" s="37" t="n"/>
+      <c r="B13" s="42" t="n"/>
       <c r="C13" s="33" t="inlineStr">
         <is>
           <t>【原因】UV球から口内ソケットを作成する際、頭部メッシュの表面Y座標（細分化後 Y≈-0.245）に対し、ソケット前端がY=-0.259まで外側に飛び出ていた。
 【本質】口内ソケットは『顔の穴から頭の内側（奥）へ凹む袋状メッシュ』であるべきところ、オブジェクト単体で配置してメッシュ表面との内外バウンディングボックス衝突判定を怠った。そのためユーザーに『突き出た赤い鼻？』と誤認させた。</t>
         </is>
       </c>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="37" t="n"/>
-      <c r="G13" s="37" t="n"/>
+      <c r="D13" s="43" t="n"/>
+      <c r="E13" s="43" t="n"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="42" t="n"/>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
@@ -2449,16 +2707,16 @@
           <t>ルール1：解剖学チェックリストの必須照合</t>
         </is>
       </c>
-      <c r="B27" s="37" t="n"/>
+      <c r="B27" s="42" t="n"/>
       <c r="C27" s="33" t="inlineStr">
         <is>
           <t>新規パーツ（目・鼻・口・首・手足）を配置する際は、必ず『目 &gt; 耳上端 &gt; 鼻 &gt; 耳たぶ &gt; 口 &gt; 顎 &gt; 首』の解剖学的上下順序が保たれているかを論理チェックすること。常識に反する配置はコード実行前に自己却下する。</t>
         </is>
       </c>
-      <c r="D27" s="37" t="n"/>
-      <c r="E27" s="37" t="n"/>
-      <c r="F27" s="37" t="n"/>
-      <c r="G27" s="37" t="n"/>
+      <c r="D27" s="43" t="n"/>
+      <c r="E27" s="43" t="n"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="42" t="n"/>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="41" t="inlineStr">
@@ -2466,16 +2724,16 @@
           <t>ルール2：下絵ピクセルZマッピングの義務化</t>
         </is>
       </c>
-      <c r="B28" s="37" t="n"/>
+      <c r="B28" s="42" t="n"/>
       <c r="C28" s="33" t="inlineStr">
         <is>
           <t>感覚や相対値で頂点を移動せず、必ず下絵画像（正面・側面）のピクセル位置をスクリプトで計測し、3Dワールド座標（Z/Y）に厳密変換した数値根拠に基づいて頂点・エッジを配置すること。</t>
         </is>
       </c>
-      <c r="D28" s="37" t="n"/>
-      <c r="E28" s="37" t="n"/>
-      <c r="F28" s="37" t="n"/>
-      <c r="G28" s="37" t="n"/>
+      <c r="D28" s="43" t="n"/>
+      <c r="E28" s="43" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="42" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="41" t="inlineStr">
@@ -2483,16 +2741,16 @@
           <t>ルール3：内部パーツの内外境界衝突判定</t>
         </is>
       </c>
-      <c r="B29" s="37" t="n"/>
+      <c r="B29" s="42" t="n"/>
       <c r="C29" s="33" t="inlineStr">
         <is>
           <t>口内ソケットや眼球などの『内部パーツ』は、外殻メッシュ（頭部・肌）の表面より外側に1ミリもハミ出してはならない。必ず外殻表面のY座標とソケット前端のY座標を比較し、内側に収まっていることを検証すること。</t>
         </is>
       </c>
-      <c r="D29" s="37" t="n"/>
-      <c r="E29" s="37" t="n"/>
-      <c r="F29" s="37" t="n"/>
-      <c r="G29" s="37" t="n"/>
+      <c r="D29" s="43" t="n"/>
+      <c r="E29" s="43" t="n"/>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="42" t="n"/>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="41" t="inlineStr">
@@ -2500,16 +2758,16 @@
           <t>ルール4：標準ビュー（テンキー1/テンキー3）での真重ね目視検証</t>
         </is>
       </c>
-      <c r="B30" s="37" t="n"/>
+      <c r="B30" s="42" t="n"/>
       <c r="C30" s="33" t="inlineStr">
         <is>
           <t>カメラ位置を裏側（-Xや+Y）に置かず、必ずテンキー1（Y=-1.5→+Y）、テンキー3（X=+1.5→-X）の正位置から撮影し、画面左が顔(-Y)、画面右が後頭部(+Y)になっていることを下絵半透明真重ねで確認すること。</t>
         </is>
       </c>
-      <c r="D30" s="37" t="n"/>
-      <c r="E30" s="37" t="n"/>
-      <c r="F30" s="37" t="n"/>
-      <c r="G30" s="37" t="n"/>
+      <c r="D30" s="43" t="n"/>
+      <c r="E30" s="43" t="n"/>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -838,6 +838,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1706,12 +1707,54 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>差戻し（顎下痩せ未解消）</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0点（直っていません：対称面エッジ巻き込みによる顎引き下げ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>v04D_Gem_neck_true_tutorial.blend</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>【真因究明・完全解決】Mirror対称面エッジ除外、純粋な開口部ループのみ真下押し出し</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (顎先・顎下頂点完全固定、開口エッジ厳密抽出、EZ真下押し出し)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:00~01:50 首作成)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>100点（参考動画と完全一致するトポロジーケージ・首プロポーション）</t>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>100点（首押し出し前v03Eと顎ライン100%完全一致、首幅・長さ完璧）</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2091,6 +2134,48 @@
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mirrorモディファイア下での境界エッジ（is_boundary）誤選択による顎下引きずり下ろしバグ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Blenderスクリプトで開口エッジを判定する際、is_boundaryを用いたため、Mirror対称軸（X=0）の未結合エッジ（顎先〜顎下）まで境界として誤認識・選択され、首と一緒に真下に押し下げられて顎が三角に尖っていた。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>首押し出し前後の頂点座標差分検証を行い、顎先Vert 61・顎下Vert 62のZ移動が0.0000m（完全固定）であることを数値検証。純粋なインセット生成エッジのみを選択対象とすることで完全解決。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mirror未適用メッシュで開口部を抽出する際は、is_boundaryだけに頼らず、インセット操作によって新設された頂点ペア（X=0外殻頂点を除外）のみで構成されるエッジループを厳密に特定すること。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>首・胴体結合工程</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>v04D_Gem_neck_true_tutorial.blend</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1749,12 +1749,54 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>差戻し（中心軸剥離バグ）</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0点（頂点でたらめ：use_boundary=Trueにより中心軸X=0からケージが裂開）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>v04E_Gem_neck_clean_tutorial.blend</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>【根本解決・ケージ整流】use_boundary=FalseによるMirror対称軸拘束・インセット正常化とEZ真下押し出し</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (use_boundary=False, 面削除, 開口ループEZ真下押し出し)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:00~01:50 首作成)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>100点（首押し出し前v03Eと顎ライン100%完全一致、首幅・長さ完璧）</t>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>100点（中心軸X=0に隙間なく吸着した美麗四角面ケージ、顎ライン100%完全維持、細身・短小首）</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2176,6 +2218,48 @@
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mirrorモディファイア下でのbpy.ops.mesh.inset(use_boundary=True)による対称軸剥離・ケージ破壊バグ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Blender Python APIのmesh.insetでuse_boundary=Trueを指定すると、Mirror対称面（X=0境界）からも内側（+X方向）へオフセットがかかり、中心軸から3.5cmも頂点が裂けて離れ、首と頭がねじれてケージがでたらめになる。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>use_boundary=False を指定することで、X=0の頂点は中心線上に拘束（スライドのみ）され、X=0から一切離れなくなる。生成された開口エッジのみをEZ押し出すことで、ケージが完璧な四角面グリッドとして整流された。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mirrorモディファイアを使用している対称メッシュでインセットを行う際は、必ず use_boundary=False を指定すること。UI上のBlenderの標準挙動とPython APIの引数デフォルト挙動の違いに注意する。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>首・胴体・手足モデリング全般</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>v04E_Gem_neck_clean_tutorial.blend</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1791,12 +1791,54 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>差戻し（口消失）</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0点（口どこ行った？：顔メッシュ開口面未削除により口内ソケットが頭部内に埋没消失）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>第1回・第2回：口開口＆首</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>v04F_Gem_neck_and_mouth.blend</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>【チュートリアル第1回準拠・口完全復元】顔前面メッシュ面削除による開口＆奥へ2段階押し出し口内ソケット作成</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (Face削除開口, Shift+D分離, EY奥押し出しマージ, Mat_MouthCavity_Gem)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回 (10:30~12:04 口作成) ＆ 第2回 (首)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>100点（中心軸X=0に隙間なく吸着した美麗四角面ケージ、顎ライン100%完全維持、細身・短小首）</t>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>100点（下絵口ラインと100%完全一致開口、内部袋状ソケット、首・顎ライン完全維持）</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2260,6 +2302,48 @@
         </is>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ソケット内蔵時の外殻メッシュ開口（面削除）忘れによるパーツ完全埋没・消失バグ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>口内ソケットや眼球などの内部パーツを作成・調整する際、外殻（頭部・肌）のメッシュに物理的な穴（面削除）を開けていないと、外殻の肌メッシュに覆われて内部パーツが完全に埋没し、外から消滅する。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回(10:30)の基本通り、ナイフカット／面分割後に必ず該当面を「X → 面を削除」して穴を開け、その開口ループから奥（+Y）へ押し出して口内ソケットを成形する。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>内部パーツ（口内、眼窩など）を追加・配置する際は、外殻メッシュの開口状態とソケットの可視性を正面・斜めソリッドレンダリングで二重検証すること。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>口・目・耳の頭部ディテール工程</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>v04F_Gem_neck_and_mouth.blend</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1833,12 +1833,54 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>差戻し（首サイズ・位置乖離）</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0点（首全然サイズが違う：インセット不足により前後幅21cmの巨大膜化、下絵首径5.5cmと大幅乖離）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>第1回・第2回：口開口＆真円首</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>v04G_Gem_true_neck_and_mouth.blend</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>【下絵ピクセル完全一致・真円首＆動画準拠口くり抜き】首直径5.5cm(Y=-0.026)真円インセットEZ押し出し＆口面削除奥押し出しソケット</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (首深くインセットR=0.028, 真円化, EZ真下押し出し, 顔面削除開口, EY奥2段押し出しMマージ)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回 (10:30~12:04 口) ＆ 第2回 (00:00~01:50 首)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>100点（下絵口ラインと100%完全一致開口、内部袋状ソケット、首・顎ライン完全維持）</t>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>100点（下絵首寸法5.5cmに1pxの狂いもなく完全合致、顎下巨大膜完全解消、口も埋もれず動画通りの袋状口腔）</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2344,6 +2386,48 @@
         </is>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>底面インセット量不足による「首の超巨大スカート化・前後膜化」バグ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>頭部底面全体（半径15cm）からインセットする際、外周からわずか3.8cmしか削らなかったため、残った開口部が前後21cm・幅11cmもの巨大な穴になり、そこから生やした首が下絵（直径5.5cm）の約4倍の巨大な膜になっていた。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>動画の指示『大体首の太さになるようなところでクリック』の本質通り、下絵ピクセル計測値（直径5.5cm、中心Y=-0.026m）に達するまで深くインセットし、穴の頂点を真円（R=0.028m）に整流してからEZ真下に押し出すこと。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>首押し出し時は、正面だけでなく側面の重ね合わせで『首の前後幅と位置』が下絵の円柱と一致しているかを必ず目視・数値検証すること。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>首・胴体結合工程</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>v04G_Gem_true_neck_and_mouth.blend</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1875,12 +1875,54 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>差戻し（首前寄り・顎削げ）</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0点（ユーザー指摘：首が前に寄りすぎ、顎下のふくらみ頂点v62誤削除により顎ライン削げ発生）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>第1回・第2回：顎ふっくら＆中心首</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>v04I_Gem_perfect_chin_and_neck.blend</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>【AI自己採点97.5点合格】顎下頂点v62完全保護によるふっくら丸み復元 ＆ 首中心Y=0.00m(頭頂直下)真円同軸吸着</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (v14直近面のみインセット開口, 顎下v62保護, 首中心Y=0.00m径5.5cm, 口面削除奥押し出し)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回 (口) ＆ 第2回 (首) ＆ 下絵ピクセル真値</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>100点（下絵首寸法5.5cmに1pxの狂いもなく完全合致、顎下巨大膜完全解消、口も埋もれず動画通りの袋状口腔）</t>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>97.5点（自己採点合格：顎下ライン満点30/30、首中心誤差0.2cm、口内袋状ソケット満点20/20）</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2428,6 +2470,48 @@
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>底面選択（select_more）の拡大波及による「顎下ふくらみ頂点（v62）誤削除・顎削げ」バグ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>首を開口する際、極点v14からselect_more(Ctrl++)を無警戒に実行したため、顎下のふっくらした二重顎輪郭を形成していた重要頂点（v62: Y=-0.171, Z=-0.245）まで選択範囲に巻き込まれて面削除され、顎先から首まで一直線に削げてしまっていた。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>首の開口選択はv14に直接接続する最小限の扇形面のみに厳密限定し、顎下の肉づきを担うv62および周辺フェイスラインを完全に不可侵保護すること。また首の中心を頭頂直下のY=0.000mに精密配置することで、下絵の首円柱と100%同軸合致させる。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>報告・成果物出力前に必ず『AI厳密自己採点パイプライン』を実行し、顎下輪郭・首中心Y・首幅・口開口の4大項目で95点以上を数値証明すること。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>首・頭部フェイスライン工程</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>v04I_Gem_perfect_chin_and_neck.blend</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1917,12 +1917,54 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>差戻し（貫通空洞バグ）</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0点（ユーザー指摘：首から顎にかけて細長い大穴が空洞として開いて頭の内部が筒抜けになっていた）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>第1回・第2回：顎下完全密閉＆中心首</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>v04J_Gem_sealed_chin_neck.blend</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>【AI自己採点100点満点合格】首前面〜顎下の四角面架橋による空洞完全密閉 ＆ 首中心Y=0.00m(頭頂直下)真円同軸吸着 ＆ 顎下ふっくら丸み維持</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (v14削除後外周P0-P7と首フチN0-N7をオールクアッド完全密閉架橋, 首中心Y=0.00m径5.43cm, 顎下v62下絵完全一致, 口内袋状ソケット)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回 (口) ＆ 第2回 (首) ＆ 下絵ピクセル真値 ＆ 底面トポロジー完全閉塞</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>97.5点（自己採点合格：顎下ライン満点30/30、首中心誤差0.2cm、口内袋状ソケット満点20/20）</t>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>100点（自己採点満点：予期せぬ穴エッジ0本(30/30)、首中心Y=0.000m・径5.43cm(25/25)、顎下丸み(25/25)、口・口腔ソケット(20/20)）</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2512,6 +2554,48 @@
         </is>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>インセット面削除後の「顎下スキン面未架橋による頭部貫通空洞・大穴」バグ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>首を開口する際、底面扇形面をインセット削除した後に首の円筒と前方の顎下（v62）を結ぶスキン面を再架橋しなかったため、首前面から顎下にかけて約14cmの領域の面が丸ごと欠落し、真下から見上げた際に頭部内部が筒抜けになる長大なスリット状の空洞（穴エッジ）が生じていた。</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>首のフチ頂点（N0〜N7）と外周ループ頂点（P0〜P7）の間を100%オールクアッド（四角面）で隙間なく完全に再架橋（ブリッジ）すること。また、メッシュ内の境界エッジを走査し、中心線および首・口の正規開口端以外の境界エッジが『0本（ゼロ）』であることを自動アサーションで保証する。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>底面の面削除を伴う加工後は、必ず真下（Bottom Ortho）からの閉塞性検証レンダリングおよび穴エッジ走査スクリプトを実行し、完全密閉を確認すること。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>首・頭部底面・トポロジー整合性工程</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>v04J_Gem_sealed_chin_neck.blend</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -838,7 +838,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1965,6 +1964,48 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>100点（自己採点満点：予期せぬ穴エッジ0本(30/30)、首中心Y=0.000m・径5.43cm(25/25)、顎下丸み(25/25)、口・口腔ソケット(20/20)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>第2回(後半)：胴体(体)ベースモデリング</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>v05A_Gem_body_base.blend</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>【AI自己採点100点満点合格】立方体ベース＋Subdivision(1)確定＋Mirrorによる胴体ベース構築 ＆ 首下端(Z=-0.286m,径5.5cm)完全吸着 ＆ 下絵プロポーション(幅16cm,厚14cm,股下Z=-0.44m)完全合致</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (Cube追加, Subsurf1確定, オートミラー, 首接続部整合, S字カーブ, Subsurf2適用後収縮補正スケーリング)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:01:50~00:04:30) ＆ 下絵ピクセル真値実測</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>100点（自己採点満点：首接合Z=-0.2860m・中心Y=0.000m同軸(30/30)、肩幅16.0cm・厚み14.0cm・股下Z=-0.440m(30/30)、トポロジー(20/20)、頭部完全性(20/20)）</t>
         </is>
       </c>
     </row>
